--- a/Jack_RPTC_tests/RPTC Comparison File uploadvsbroad.xlsx
+++ b/Jack_RPTC_tests/RPTC Comparison File uploadvsbroad.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woodj\Documents\cidy\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woodj\Documents\cidy\Jack_RPTC_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB569D38-9ADC-4794-9249-5FC6BA7DA9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78959B30-DC9D-4008-B940-D587116A11CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{F62C9E2E-E7EF-4424-B0AF-B8E2F95C1F3D}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" activeTab="2" xr2:uid="{F62C9E2E-E7EF-4424-B0AF-B8E2F95C1F3D}"/>
   </bookViews>
   <sheets>
-    <sheet name="File Upload" sheetId="1" r:id="rId1"/>
+    <sheet name="File Upload narrow-broad" sheetId="1" r:id="rId1"/>
     <sheet name="Broad Only" sheetId="2" r:id="rId2"/>
+    <sheet name="File Upload broad-narrow" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="104">
   <si>
     <t>Scenario</t>
   </si>
@@ -337,12 +338,6 @@
   </si>
   <si>
     <t>How are RPTC activities planned, approved, revised, and reported after completion?</t>
-  </si>
-  <si>
-    <t>Happy path - RPTC 2024 achievements [RPTC]</t>
-  </si>
-  <si>
-    <t>What were the main achievements of the Regular Programme of Technical Cooperation in 2024?</t>
   </si>
   <si>
     <t>Happy path - RPTC 2024 countries requests interventions [RPTC]</t>
@@ -835,6 +830,230 @@
   <si>
     <t>Poor</t>
   </si>
+  <si>
+    <t>foundanswer2</t>
+  </si>
+  <si>
+    <t>Answer: The budget and finance requirements for the Regular Programme of Technical Cooperation (RPTC) are as follows:
+Funding Source: RPTC is funded from Section 23 of the UN’s Regular Budget. Implementing entities have flexibility in using appropriated financial resources, provided activities align with the United Nations Strategic Framework and programme priorities presented in the Programme Budget. Resource allocation decisions are made by implementing entities, guided by their governing or advisory bodies. Activities are expected to be delivered within a relatively short timeframe, usually less than two calendar years.
+Proposal and Approval Process: Activities must be documented in an RPTC Activity Proposal, which includes project ID, budget, timeframe, geographic scope, country demand, SDG links, themes, target groups, capacities to be developed, timelines, coherence with other work, inclusion considerations, inputs, and financial requirements. The proposal is reviewed by CDPMO, which may request additional documentation or revisions. The budget should effectively support the achievement of intended results and be used for activities with clearly identified capacity development outcomes.
+Criteria for Activities: Activities should be responsive to the demand of developing countries, be of a short-term nature (conceived and implemented within less than one calendar year), and fall within DESA’s priority areas. Longer-term initiatives may continue if external resources are mobilized. Activities should build capacity in developing countries and may aid in preparing requests for larger-scale funding from other sources. Cost-sharing is encouraged, especially for countries that are not least developed, including in-kind contributions to ensure buy-in and ownership.
+Budget Changes: If divisions wish to change the budget, increases less than 10% or $10,000 can be made without a formal request; larger increases require a revised proposal outlining reasons, achievements, impact, and revised budget. Changes in objectives or strategy require a new proposal.
+Exclusions: RPTC does not fund travel to conferences, meetings, or events that are normative or inter-governmental in nature.
+Sources:
+​rptc_1st_progress_report.pdf​
+​Readme.txt​
+​rptc_guidelines_20233.docx​
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">general to guidance </t>
+  </si>
+  <si>
+    <t>Answer: The programme design standards for the Regular Programme of Technical Cooperation (RPTC) are outlined in the internal guidance and templates provided for DESA RPTC activities. Key standards include:
+Use of an RPTC activity proposal template, which documents project ID, budget, timeframe, geographic scope, country demand, SDG links, themes, target groups, capacities to be developed, timelines, coherence with other work, inclusion considerations, inputs, and financial requirements.
+Application of common reporting standards that define minimum RPTC data points, output categories, geographic coverage, participant and beneficiary tracking, outreach, complementarity with DA/XB projects, and Programme Monitoring Tool recommendations.
+Adherence to broader RPTC guidelines explaining the programme’s purpose, demand-driven nature, eligible short-term capacity-development uses, planning and approval process, proposal revisions, Inter-Regional Adviser use, and post-activity reporting requirements.
+Integration of Common Reporting Standards (CRS) agreed by Implementing Entities (IEs) to address simplification of reporting, standardization of terminology, treatment of country support (national, sub-regional, regional, global), monitoring of virtual support, attribution of impact, monitoring of events (workshops, trainings), and alignment of Programme Monitoring Tools for consistent data capture.
+These standards are designed to ensure coherence, comparability, and quality in RPTC programme design, implementation, and reporting. The CRS are a recent development and are being integrated into templates and practices, with full benefits expected in the upcoming reporting cycle. The standards also emphasize demand-driven, government-led initiatives and sustainability through local and national ownership, knowledge transfer, and capacity enhancement, especially via South-South cooperation.
+Sources:
+​Readme.txt​
+​eighth_progress_report_of_the_rptc_2022_final_1.pdf​
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>Answer: You are seeking guidance on drafting an evaluation report for a project under the RPTC, specifically focusing on process, structure, and recommended practices.
+Step-by-Step Guidance for Writing an RPTC Evaluation Report:
+Follow Common Reporting Standards (CRS):
+Use a centralized template for capturing data, as recommended by DESA. This ensures systematic and comparable data collection, simplifying the reporting process and enhancing the assessment of effectiveness. The template should cover outreach, deliverables, and impact of activities.
+Incorporate Lessons Learned:
+Reference previous activities and evaluations to inform your report. Highlight how past insights have shaped current interventions, such as improvements in data management, workshop evaluations, and feedback mechanisms.
+Structure Your Report:
+Introduction: Briefly describe the project, its objectives, and context within RPTC.
+Methodology: Explain the evaluation approach, including data sources, tools (e.g., surveys, feedback forms), and criteria for assessment.
+Results: Present findings using performance indicators, baseline and target figures, and qualitative feedback from participants or stakeholders. Include sex-disaggregated data where possible.
+Analysis: Discuss the achievement of expected accomplishments, quality, timeliness, and budget compliance. Assess development impact, referencing longer-term objectives such as capacity development and alignment with SDGs.
+Lessons Learned: Summarize key insights and recommendations for future activities, referencing how previous evaluations have informed improvements.
+Conclusion: Provide a concise summary of outcomes, challenges, and recommendations for ongoing or future projects.
+Use Unified Evaluation Templates:
+If available, apply unified templates enforced by your entity (e.g., ESCWA’s approach), ensuring comparability and consistency across subprograms. Record whether evaluations were undertaken in the tracking system.
+Ensure Timely and Stable Reporting:
+Finalize and maintain reporting templates for at least three years, submitting them alongside RPTC fund allocations. Focus annual reporting on quantitative data and essential programmatic information.
+Reference OIOS Recommendations:
+Assess or evaluate contributions using a combination of RPTC-specific performance indicators, broader evaluations, and sample assessments of support interventions. Consider evaluating a sample of interventions over a 3–5 year period for a thorough assessment of intermediate outcomes.
+Practical Example:
+DESA’s centralized template and ESCWA’s unified evaluation templates are practical tools for ensuring systematic data capture and comparability. UNCTAD’s use of post-workshop surveys and OHCHR’s integration of training processes based on past challenges are examples of embedding lessons learned into evaluation reports.
+Challenges:
+Tracking contributions to outcomes can be difficult, especially for small-scale or urgent activities. Providing sex-disaggregated data for virtual/hybrid events may require improved systems and coordination with partners.
+Sources:
+​ninth_progress_report_of_the_rptc_2023.pdf​
+rptc_1st_progress_report.pdf
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>Answer: An RPTC activity proposal template requires the following information:
+Activity Details:
+Title of the activity
+Planned start quarter and year
+Planned end date
+Description of proposed activities (e.g., training workshops, advisory services, study tours, capacity building tools)
+Draft programme/agenda as annex for applicable activities
+Draft terms of reference for consultants/resource persons as annex, if available
+Detailed timeline if activities span more than three months
+Coherence and Complementary Work:
+Relationship to existing or proposed projects funded by the Development Account or extrabudgetary resources
+Description of other work addressing the same problem and how the RPTC activity adds value
+Linkages with ongoing complementary work (e.g., joint work plan, UNSDCF Joint Output)
+Gender Equality, Human Rights, Disability Inclusion, Leave No One Behind:
+Analysis prepared to inform how the activity advances these agendas
+Description of how the activity will take the analysis into account
+Systematic tagging and ratings for gender and disability (scale from 0 to 2b)
+Inputs:
+Specific inputs (cash and in-kind) provided by DESA, recipient governments, and other stakeholders
+Comments for each input
+Nature of Demand:
+Type of demand (Request, Voluntary National Review, UN Sustainable Development Cooperation Framework, Other)
+Meeting Type and Venue:
+Meeting type (in person, virtual, N/A)
+Venue location (country, city) if in person
+Problem Analysis:
+Concise description of the problem the activity addresses
+DESA Mandate and Expected Results:
+Main mandates for the work
+Contribution of the activity to implementing division priorities
+Expected results and performance measures, referencing Programme Budget Section 9
+Recipient Country Request:
+Indication if the activity responds to a direct country request
+Evidence of demand from target countries (e.g., UNSDCF outcome, VNR, needs assessments)
+Signatures:
+Name and signature of Director/Division
+Name and signature of Head/Capacity Development Programme Management Office
+Additional Information:
+Any other relevant information (optional)
+This structure ensures comprehensive documentation for planning, approval, and implementation of RPTC activities.
+Sources:
+​rptc_activity_proposal_template_docx_2 (1).docx​
+Confidence: High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Sent at June 24 at 2:41 PM
+Bot said: debug:User question: What should be captured in an RPTC activity report template after an activity? Message is interactive. Click to interact.
+Bot said:
+Answer: The RPTC activity report template should include the following information and reporting requirements after an activity:
+Activity Dates: Clearly specify the dates (range) of the advisory service or activity.
+Budget Consumed: Document the budget used for the activity.
+RPTC/IRA Links: Indicate connections to RPTC and Inter-Regional Adviser (IRA) involvement.
+Countries Supported: List countries supported, disaggregated by SIDS (Small Island Developing States), LDCs (Least Developed Countries), and LLDCs (Landlocked Developing Countries).
+Resident Coordinator Consultation: Note any consultations with Resident Coordinators.
+Activity Type: Specify the type of activity (e.g., training, workshop, advisory service).
+Participants: Record the number of participants, disaggregated by gender and country of origin.
+Co-financing: Indicate any co-financing arrangements.
+Immediate Results: Capture immediate results and outcomes, including policy or strategy outcomes.
+Inclusion and Sustainability: Address inclusion considerations and sustainability aspects.
+Collaboration and Outreach: Document collaboration with other partners and outreach conducted.
+Lessons Learned: Include lessons learned from the activity.
+Annexes: Attach relevant annexes such as evaluation forms and supporting documents.
+Additional requirements:
+Participant Feedback: Collect and report feedback from participants to track the direct impact of support and capacity improvement.
+Evaluation Forms: Maintain a record of evaluation forms completed by participants, indicating how the activity met their expectations and addressed capacity needs.
+Number and Days of Events: Report the number of events and the number of days for each event.
+Target Audience: Specify the target audience (e.g., government, private sector, civil society).
+Collaboration with Other Partners: Provide information on cooperation with other UN system entities and stakeholders.
+Divisions are encouraged to use online forms for better analysis and statistics over time and to ensure reporting aligns with the RPTC Common Reporting Standards, which include standardized terminology and key data points for monitoring and reporting. The template should facilitate systematic capture and analysis of crucial data on outreach, deliverables, and impact, enhancing the ability to assess effectiveness and lessons learned for future activities.
+Sources:
+​Readme.txt​
+​rptc_guidelines_20233.docx​
+​annex_4_common_reporting_standards_.pdf​
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>Answer: Planning of RPTC Activities:
+Divisions prepare Programme Budgets for RPTC annually, aligning with the Regular Budget cycle.
+Activities are programmed in the first quarter or phased throughout the budget period to optimize resource use and respond to urgent Member State requests.
+Divisions submit a work plan before the calendar year starts, identifying indicative and emerging country needs.
+When responding to requests, divisions assess alignment with mandates, beneficiary country status (especially LDCs, LLDCs, SIDS), available resources, and potential development outcomes.
+Demand can arise from direct country requests, needs identified through VNRs, CCAs, technical assessments, or intergovernmental mandates.
+Priority is given to direct country requests, but other types of demand are also eligible.
+Proposals for funding individual activities are submitted to CDPMO for approval using the RPTC Activity Proposal Template, documenting project details such as budget, timeframe, geographic scope, SDG links, target groups, and more.
+Approval Process:
+CDPMO reviews proposals against criteria: responsiveness to developing country demand, short-term nature, alignment with DESA priorities, capacity-building focus, and catalytic potential for longer-term assistance.
+CDPMO considers division performance and human resource capacity.
+Budget must support intended results and be used effectively.
+Joint proposals across divisions are possible, requiring a lead division and coordinated management arrangements.
+Cost-sharing is encouraged, especially for non-LDC countries, to ensure ownership.
+Revision of RPTC Activity Proposals:
+Divisions submit written requests to CDPMO for changes to approved proposals.
+Budget changes: If increase is less than 10% or $10,000, CDPMO can adjust without formal request; larger increases require a revised proposal explaining reasons, achievements, impact, and revised budget.
+Objective/strategy changes: Require a new proposal.
+Timing/duration changes: No formal request needed if within three months, but CDPMO must be notified.
+Implementation arrangement changes (e.g., venue): No formal request needed, but CDPMO must be notified.
+Reporting After Completion:
+Divisions must submit RPTC Activity Reports (using the template) within two weeks of activity completion.
+A datasheet is completed for each activity; the remainder of the report can cover related activities from the same proposal.
+Records of training activities must include event details, participant numbers (by gender and country), and evaluation forms.
+Evaluation forms should assess whether the activity met expectations and addressed capacity needs; online forms are encouraged for analysis.
+Reporting includes countries supported (disaggregated by SIDS, LDCs, LLDCs), outreach, types of support, and must align with RPTC Common Reporting Standards.
+Feedback on results achieved is encouraged for Programme Budget and annual progress reporting.
+Sources:
+​Readme.txt​
+​rptc_guidelines_20233.docx​
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>Answer: In 2024, the Regular Programme of Technical Cooperation (RPTC) supported the following:
+Countries Supported: 169 countries received support using RPTC funds, with 147 countries assisted at the national level. This included 36 Least Developed Countries (LDCs), 26 Landlocked Developing Countries (LLDCs), and 34 Small Island Developing States (SIDS).
+Requests: Implementing Entities (IEs) received a total of 1164 requests for assistance and responded to 1040 of these with RPTC interventions.
+Interventions: There were 2614 RPTC interventions across all levels (national, sub-regional, regional, and global).
+People Supported: 78,343 people were reached through RPTC activities, including 37,930 women.
+Sources:
+​tenth_progress_report_of_the_regular_programme_of_technical_cooperation.pdf​
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>general to progress reports</t>
+  </si>
+  <si>
+    <t>Second try: Answer: The following UN implementing entities delivered activities under the Regular Programme of Technical Cooperation (RPTC): DESA, UNCTAD, UN-Habitat, UNODC, OCHA, OHCHR, ECA, ESCAP, ECE, ECLAC, and ESCWA. Their results and performance varied based on the nature of interventions and improvements in monitoring and evaluation systems:
+DESA: Focused on capacity building, such as developing the National Forest Financing strategy in Suriname and training statistical officers in Uruguay. DESA also refined performance indicators and embedded them in reporting templates, ensuring systematic capture and reporting of outcomes.
+UNCTAD: Supported national strategies like Ghana’s E-commerce Strategy and increased negotiation capacities for WTO LDC Group Delegates across multiple countries.
+UN-Habitat: Provided technical advisory services for spatial development concepts and supported sustainable urbanisation recommendations.
+UNODC: Developed national anti-corruption strategies and supported justice access workshops.
+OCHA: Conducted community consultations to identify humanitarian priorities.
+OHCHR: Offered technical advisory services for establishing national human rights institutions and forensic assistance for human rights violations.
+ECA: Empowered communities through digital ID and innovation, and strengthened demographic-sensitive budgeting.
+ESCAP: Developed frameworks for electric mobility and enhanced capacity for inclusive evidence-based reporting.
+ECE: Developed national statistical indicator systems and environmental reporting.
+ECLAC: Supported rural development plans and updated policies for national development frameworks.
+ESCWA: Assisted in preparing national reports on international platforms.
+Performance improvements were noted in monitoring and evaluation (M&amp;E) systems, data quality, and reporting mechanisms. Entities like UNODC devised specific indicators for interventions, ESCAP adopted the UN’s IPMR for result tracking, ECE developed tools for capturing technical cooperation requests, and DESA embedded refined performance indicators in reporting templates. These enhancements led to better alignment with reporting requirements and more systematic outcome capture. Many entities also acted on recommendations from previous progress reports to strengthen their M&amp;E, enabling more effective outcome tracking and reporting.
+Sources:
+​tenth_progress_report_of_the_regular_programme_of_technical_cooperation.pdf​
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>Answer: Challenges Identified by the RPTC Progress Report (2024):
+Lack of common understanding between Implementing Entities (IEs) and the Advisory Committee on Administrative and Budgetary Questions (ACABQ) regarding the nature of RPTC.
+Issues with implementing a common approach among IEs around outreach, contribution to outcomes, and geographic scope.
+Limited visibility of data over time, making it difficult to track the evolution of RPTC and identify gaps in countries served.
+Some countries are better positioned to receive RPTC support, resulting in uneven distribution of assistance.
+Ongoing financial complications due to the UN liquidity crisis, requiring IEs to operate within reduced spending ceilings and respond to increasing demands with limited resources.
+Recommendations for Strengthening RPTC:
+Ensure shared understandings across the UN, especially between IEs and ACABQ, regarding RPTC’s nature, outreach, and outcomes.
+Focus on analyzing data over time and act on this analysis to identify underserved countries and improve targeted outreach.
+Develop clear principles and guidelines to guide decision-making during financial uncertainty, including prioritization of funds for technical cooperation in priority areas or underserved Member States.
+Consider producing the RPTC Progress Report every three years to enhance visibility and tracking of progress.
+These recommendations aim to improve coherence, data analysis, targeted outreach, and financial decision-making for future RPTC activities.
+Sources:
+​tenth_progress_report_of_the_regular_programme_of_technical_cooperation.pdf​
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>to PD - country data again</t>
+  </si>
 </sst>
 </file>
 
@@ -862,7 +1081,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -884,6 +1103,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -944,11 +1169,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1287,7 +1529,611 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13893492-342B-4CC0-810B-527A63DE0465}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="45.44140625" customWidth="1"/>
+    <col min="4" max="5" width="32.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="11" width="12.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <f t="shared" ref="B2:B18" si="0">MID(A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))+1,FIND("]",A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[","")))))-FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))-1)</f>
+        <v>RPTC</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H1:K18">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="no">
+      <formula>NOT(ISERROR(SEARCH("no",H1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="yes">
+      <formula>NOT(ISERROR(SEARCH("yes",H1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CD0A4D-515F-4116-8764-EC2E5F09246B}">
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.33203125" customWidth="1"/>
@@ -1325,10 +2171,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
@@ -1336,25 +2182,25 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="str">
-        <f t="shared" ref="B2:B19" si="0">MID(A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))+1,FIND("]",A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[","")))))-FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))-1)</f>
+        <f t="shared" ref="B2:B18" si="0">MID(A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))+1,FIND("]",A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[","")))))-FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))-1)</f>
         <v>RPTC</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -1366,26 +2212,26 @@
         <v>11</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -1396,29 +2242,29 @@
       <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
+      <c r="D4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>20</v>
       </c>
@@ -1430,28 +2276,26 @@
         <v>21</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>67</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E5" s="8"/>
       <c r="F5" s="8" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -1462,29 +2306,27 @@
       <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="D6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>25</v>
       </c>
@@ -1496,26 +2338,26 @@
         <v>26</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="8"/>
+        <v>27</v>
+      </c>
+      <c r="E7" s="10"/>
       <c r="F7" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -1526,27 +2368,29 @@
       <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="5" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>31</v>
       </c>
@@ -1558,26 +2402,26 @@
         <v>32</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>34</v>
       </c>
@@ -1591,20 +2435,26 @@
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="H10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>37</v>
       </c>
@@ -1616,28 +2466,26 @@
         <v>38</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>74</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
@@ -1649,26 +2497,26 @@
         <v>41</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>43</v>
       </c>
@@ -1679,212 +2527,191 @@
       <c r="C13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="8"/>
+      <c r="D13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F13" s="8" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="336.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>63</v>
+      <c r="D18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H1:J19">
+  <conditionalFormatting sqref="H1:J18">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="no">
       <formula>NOT(ISERROR(SEARCH("no",H1)))</formula>
     </cfRule>
@@ -1896,9 +2723,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CD0A4D-515F-4116-8764-EC2E5F09246B}">
-  <dimension ref="A1:J25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E817180-B442-4265-BD2C-656F2B3BB3D9}">
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.33203125" customWidth="1"/>
@@ -1907,10 +2734,18 @@
     <col min="4" max="5" width="32.33203125" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="10" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1930,192 +2765,232 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <f t="shared" ref="B2:B18" si="0">MID(A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))+1,FIND("]",A2,FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[","")))))-FIND("@",SUBSTITUTE(A2,"[","@",LEN(A2)-LEN(SUBSTITUTE(A2,"[",""))))-1)</f>
+        <v>RPTC</v>
+      </c>
       <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="6"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5" t="s">
-        <v>86</v>
-      </c>
+      <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
       <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>87</v>
-      </c>
+      <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
       <c r="C5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>13</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
       <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>17</v>
+      <c r="D6" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>86</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1</v>
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="10"/>
+        <v>17</v>
+      </c>
+      <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>13</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G7" s="10"/>
       <c r="H7" s="8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B8" s="5" t="str">
-        <f t="shared" ref="B8:B25" si="0">MID(A8,FIND("@",SUBSTITUTE(A8,"[","@",LEN(A8)-LEN(SUBSTITUTE(A8,"[",""))))+1,FIND("]",A8,FIND("@",SUBSTITUTE(A8,"[","@",LEN(A8)-LEN(SUBSTITUTE(A8,"[","")))))-FIND("@",SUBSTITUTE(A8,"[","@",LEN(A8)-LEN(SUBSTITUTE(A8,"[",""))))-1)</f>
+        <f t="shared" si="0"/>
         <v>RPTC</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>30</v>
-      </c>
+      <c r="D8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>87</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B9" s="8" t="str">
         <f t="shared" si="0"/>
@@ -2125,28 +3000,29 @@
         <v>32</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>89</v>
-      </c>
+      <c r="I9" s="8"/>
       <c r="J9" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -2158,28 +3034,27 @@
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B11" s="8" t="str">
         <f t="shared" si="0"/>
@@ -2189,28 +3064,29 @@
         <v>38</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="E11" s="9"/>
       <c r="F11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>13</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G11" s="8"/>
       <c r="H11" s="8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -2220,28 +3096,29 @@
         <v>41</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>89</v>
-      </c>
+      <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B13" s="8" t="str">
         <f t="shared" si="0"/>
@@ -2250,278 +3127,185 @@
       <c r="C13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="312.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="372.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="9" t="s">
+      <c r="B17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="D17" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="K17" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RPTC</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>RPTC</v>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H1:J19">
+  <conditionalFormatting sqref="H1:K18">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="no">
       <formula>NOT(ISERROR(SEARCH("no",H1)))</formula>
     </cfRule>
